--- a/Data/Bronze/MCIC-PROFUNDIZACION/Plan de mejoramiento/Entregables Plan de Mejoramiento.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Plan de mejoramiento/Entregables Plan de Mejoramiento.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udistritaleduco-my.sharepoint.com/personal/gsalazarm_udistrital_edu_co/Documents/Monitoria 2024-3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udistritaleduco-my.sharepoint.com/personal/mcic_investigacion_udistrital_edu_co/Documents/MCIC.INVESTIGACION/Plan de Mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{61232136-B4FC-4753-9E5D-EED2ECF66D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BA3484-85EF-46FD-A1B4-F72EB04A1BA9}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{61232136-B4FC-4753-9E5D-EED2ECF66D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{589B2310-7B68-4CC3-9E11-A8693C98718D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{7520C2C4-3F88-47AB-A628-6012ADE2DBDE}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{7520C2C4-3F88-47AB-A628-6012ADE2DBDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="80">
   <si>
     <t>PLAN DE MEJORAMIENTO</t>
   </si>
@@ -189,13 +189,100 @@
   </si>
   <si>
     <t xml:space="preserve">Solicitar informes periódicos sobre el avance de la obra de nueva infraestructura de la Facultad de Ingeniería a las instancias lideres del proceso.   </t>
+  </si>
+  <si>
+    <t>Incompleta</t>
+  </si>
+  <si>
+    <t>Sin iniciar</t>
+  </si>
+  <si>
+    <t>REITERE DE RADIACIÓN PEP / 2024</t>
+  </si>
+  <si>
+    <t>Soportes adicionales / actualizacion pagina web</t>
+  </si>
+  <si>
+    <t>Pedirsela al decano, para saber q docentes han participado en jornadas / incluir en formulario</t>
+  </si>
+  <si>
+    <t>B DEPENDE DE A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualizar BD </t>
+  </si>
+  <si>
+    <t>Finalizada</t>
+  </si>
+  <si>
+    <t>El SGA da la info de egresados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encuesta de autoevaluacion </t>
+  </si>
+  <si>
+    <t>Buscar cvlac para publicaciones</t>
+  </si>
+  <si>
+    <t>ACTUALIZACION SYLLABUS</t>
+  </si>
+  <si>
+    <t>B CON A</t>
+  </si>
+  <si>
+    <t>Con  BD</t>
+  </si>
+  <si>
+    <t>EXCLUSIONES</t>
+  </si>
+  <si>
+    <t>CON SGA DE EGRESADOS</t>
+  </si>
+  <si>
+    <t>Solicitar a urelinter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b con a</t>
+  </si>
+  <si>
+    <t>codirecciones / convenios</t>
+  </si>
+  <si>
+    <t>listas de asistencia</t>
+  </si>
+  <si>
+    <t>Listas de asistencia, correso eletronciso divulgacion de grupos</t>
+  </si>
+  <si>
+    <t>NUXEO</t>
+  </si>
+  <si>
+    <t>Listas de asistencia de estudiante snuevos /correos y rs</t>
+  </si>
+  <si>
+    <t>encuesta / evaluacion docente y estudiantes</t>
+  </si>
+  <si>
+    <t>Remtiri solciitud a bibliotecas - planestic ( se requiere saber cuantos docentes usan moodle) y formulario de docentes</t>
+  </si>
+  <si>
+    <t>NO TIENE NO EXISTE</t>
+  </si>
+  <si>
+    <t>REUNIONES D BIENVENIDA CON ANTIGUOS INFORMES DE SEGUIMIENTOS</t>
+  </si>
+  <si>
+    <t>ETC.</t>
+  </si>
+  <si>
+    <t>PONDERACION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,10 +749,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -690,11 +777,11 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -710,11 +797,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1048,19 +1135,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03EC64B2-0FD8-4891-9B6C-35DBD600B541}">
-  <dimension ref="B1:E37"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="B1:F37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="10.81640625" style="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="58.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="1"/>
+    <col min="3" max="3" width="58.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15" thickBot="1"/>
-    <row r="2" spans="2:5" ht="15" thickBot="1">
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="27" t="s">
         <v>0</v>
       </c>
@@ -1068,7 +1156,7 @@
       <c r="D2" s="28"/>
       <c r="E2" s="29"/>
     </row>
-    <row r="3" spans="2:5" ht="15" thickBot="1">
+    <row r="3" spans="2:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="21" t="s">
         <v>1</v>
       </c>
@@ -1082,285 +1170,406 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="26"/>
+      <c r="D4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="25"/>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="26"/>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="25"/>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="2:5" ht="15" thickBot="1">
-      <c r="B7" s="25"/>
+    <row r="7" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="26"/>
       <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:5" ht="15" thickBot="1">
+    <row r="8" spans="2:5" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20"/>
-    </row>
-    <row r="9" spans="2:5" ht="29.1">
+      <c r="D8" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B9" s="30" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="10" spans="2:5" ht="29.45" thickBot="1">
+      <c r="D9" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="29" x14ac:dyDescent="0.35">
       <c r="B10" s="31"/>
       <c r="C10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" spans="2:5">
+      <c r="D10" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="24" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="2:5" ht="29.1">
-      <c r="B12" s="26"/>
+      <c r="D11" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B12" s="25"/>
       <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="2:5" ht="29.1">
-      <c r="B13" s="26"/>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B13" s="25"/>
       <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="2:5" ht="43.5">
-      <c r="B14" s="26"/>
+    <row r="14" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="25"/>
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="2:5" ht="15" thickBot="1">
-      <c r="B15" s="25"/>
+      <c r="D14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="26"/>
       <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="2:5" ht="29.1">
+      <c r="D15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="29" x14ac:dyDescent="0.35">
       <c r="B16" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="2:5" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B17" s="25"/>
+      <c r="D16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="26"/>
       <c r="C17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="2:5" ht="29.1">
+      <c r="D17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="29" x14ac:dyDescent="0.35">
       <c r="B18" s="24" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="2:5" ht="57.95">
-      <c r="B19" s="26"/>
+      <c r="D18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="25"/>
       <c r="C19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="2:5" ht="28.5" customHeight="1" thickBot="1">
-      <c r="B20" s="25"/>
+      <c r="D19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="26"/>
       <c r="C20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="2:5">
+      <c r="D20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="24" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="2:5" ht="43.5">
-      <c r="B22" s="26"/>
+      <c r="D21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="25"/>
       <c r="C22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="2:5" ht="57.95">
-      <c r="B23" s="26"/>
+      <c r="E22" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="25"/>
       <c r="C23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="2:5" ht="43.5">
-      <c r="B24" s="26"/>
+      <c r="D23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="25"/>
       <c r="C24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="2:5" ht="29.45" thickBot="1">
-      <c r="B25" s="25"/>
+      <c r="D24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="26"/>
       <c r="C25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="2:5" ht="43.5">
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B26" s="24" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="2:5" ht="44.1" thickBot="1">
-      <c r="B27" s="25"/>
+      <c r="D26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B27" s="26"/>
       <c r="C27" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" spans="2:5" ht="29.1">
+      <c r="D27" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="29" x14ac:dyDescent="0.35">
       <c r="B28" s="24" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="2:5" ht="44.1" thickBot="1">
-      <c r="B29" s="25"/>
+      <c r="D28" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B29" s="26"/>
       <c r="C29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" spans="2:5" ht="29.1">
+      <c r="D29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="29" x14ac:dyDescent="0.35">
       <c r="B30" s="24" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="2:5" ht="58.5" thickBot="1">
-      <c r="B31" s="25"/>
+      <c r="D30" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="B31" s="26"/>
       <c r="C31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="2:5" ht="43.5">
+      <c r="D31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="24" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="2:5" ht="43.5">
-      <c r="B33" s="26"/>
+      <c r="D32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="25"/>
       <c r="C33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="2:5" ht="43.5">
-      <c r="B34" s="26"/>
+      <c r="F33" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="25"/>
       <c r="C34" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="2:5" ht="29.45" thickBot="1">
-      <c r="B35" s="25"/>
+      <c r="F34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="26"/>
       <c r="C35" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="7"/>
+      <c r="D35" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="2:5" ht="29.1">
+    <row r="36" spans="2:6" ht="29" x14ac:dyDescent="0.35">
       <c r="B36" s="24" t="s">
         <v>48</v>
       </c>
@@ -1370,8 +1579,8 @@
       <c r="D36" s="13"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="2:5" ht="44.1" thickBot="1">
-      <c r="B37" s="25"/>
+    <row r="37" spans="2:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B37" s="26"/>
       <c r="C37" s="6" t="s">
         <v>50</v>
       </c>
@@ -1380,6 +1589,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B36:B37"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B21:B25"/>
     <mergeCell ref="B2:E2"/>
@@ -1387,21 +1601,16 @@
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B36:B37"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Sin iniciar"</formula>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Finalizada"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Incompleta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Finalizada"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Sin iniciar"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
